--- a/Deliverables/Bracelet(Main)/BOM/Bracelet_Main PCB-(LSCS).xlsx
+++ b/Deliverables/Bracelet(Main)/BOM/Bracelet_Main PCB-(LSCS).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Main)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4118BE73-9157-4BD3-81E5-914988BA26EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4811C3C1-D2C4-45D6-9230-B51D351E4C78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="321">
   <si>
     <t>S. No.</t>
   </si>
@@ -847,15 +847,6 @@
   </si>
   <si>
     <t>C270678</t>
-  </si>
-  <si>
-    <t>WinSource</t>
-  </si>
-  <si>
-    <t>Available to backorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onlinecomponent </t>
   </si>
   <si>
     <t xml:space="preserve">CAP CER 0.1UF 25V X5R 0201
@@ -1002,21 +993,6 @@
     <t>0201WMF9532TCE</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount issue need quoat to local supplier </t>
-  </si>
-  <si>
-    <t xml:space="preserve">250 stock but 750 moq Amount issue need quoat to local supplier </t>
-  </si>
-  <si>
-    <t>Chipmall</t>
-  </si>
-  <si>
-    <t>MOQ 22 Amount issue need quoat to local supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need quoat to local supplier </t>
-  </si>
-  <si>
     <t>-------------</t>
   </si>
   <si>
@@ -1024,6 +1000,15 @@
   </si>
   <si>
     <t>-------</t>
+  </si>
+  <si>
+    <t>Local supplier rates</t>
+  </si>
+  <si>
+    <t>Local supplier rates/Astimated time 2-3 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local supplier rates/Manufacturer has change </t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1104,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1150,14 +1135,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1261,19 +1240,346 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1287,27 +1593,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1317,12 +1602,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1339,9 +1618,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1350,66 +1626,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1427,14 +1683,278 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1721,3141 +2241,3190 @@
   <dimension ref="A1:S56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="45" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="63.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="43" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="9.140625" style="1"/>
+    <col min="25" max="25" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="57"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="35"/>
     </row>
     <row r="2" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>277</v>
-      </c>
-      <c r="D3" s="31" t="s">
+      <c r="C3" s="111" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="I3" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J3" s="23" t="s">
+      <c r="I3" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="J3" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="48">
         <v>150</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="49">
         <v>24</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="48">
         <f>L3*5</f>
         <v>120</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="51">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="51">
         <f>O3*L3</f>
         <v>0.14400000000000002</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="51">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="52">
         <f>Q3*K3</f>
         <v>0.9</v>
       </c>
-      <c r="S3" s="5"/>
+      <c r="S3" s="53"/>
     </row>
     <row r="4" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="24">
         <v>2</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="32" t="s">
+      <c r="B4" s="125"/>
+      <c r="C4" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" s="23" t="s">
+      <c r="I4" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="3">
         <v>50</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="3">
         <f t="shared" ref="M4:M52" si="0">L4*5</f>
         <v>5</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O4" s="22">
+      <c r="O4" s="11">
         <v>3.8E-3</v>
       </c>
-      <c r="P4" s="22">
-        <f t="shared" ref="O4:Q48" si="1">O4*L4</f>
+      <c r="P4" s="11">
+        <f t="shared" ref="P4:P47" si="1">O4*L4</f>
         <v>3.8E-3</v>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4" s="11">
         <v>3.8E-3</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="5">
         <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
         <v>0.19</v>
       </c>
-      <c r="S4" s="5"/>
+      <c r="S4" s="54"/>
     </row>
     <row r="5" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="125"/>
+      <c r="C5" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J5" s="23" t="s">
+      <c r="I5" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="3">
         <v>50</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>1</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="11">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="11">
         <f t="shared" si="1"/>
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="11">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="5">
         <f t="shared" si="2"/>
         <v>0.185</v>
       </c>
-      <c r="S5" s="5"/>
+      <c r="S5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="24">
         <v>4</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6" s="23" t="s">
+      <c r="B6" s="125"/>
+      <c r="C6" s="113" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="I6" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J6" s="23" t="s">
+      <c r="I6" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="3">
         <v>40</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>6</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="11">
         <v>2.7300000000000001E-2</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="11">
         <f t="shared" si="1"/>
         <v>0.1638</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="11">
         <v>2.7300000000000001E-2</v>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="5">
         <f t="shared" si="2"/>
         <v>1.0920000000000001</v>
       </c>
-      <c r="S6" s="5"/>
+      <c r="S6" s="54"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="24">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="125"/>
+      <c r="C7" s="113" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="I7" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="3">
         <v>30</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>5</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="11">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="11">
         <f t="shared" si="1"/>
         <v>0.2455</v>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7" s="11">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="5">
         <f t="shared" si="2"/>
         <v>1.4729999999999999</v>
       </c>
-      <c r="S7" s="5"/>
+      <c r="S7" s="54"/>
     </row>
     <row r="8" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="24">
         <v>6</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="32" t="s">
+      <c r="B8" s="125"/>
+      <c r="C8" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J8" s="23" t="s">
+      <c r="I8" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="3">
         <v>10</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>1</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="11">
         <v>4.07E-2</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="11">
         <f t="shared" si="1"/>
         <v>4.07E-2</v>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="11">
         <v>4.07E-2</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="5">
         <f t="shared" si="2"/>
         <v>0.40700000000000003</v>
       </c>
-      <c r="S8" s="5"/>
+      <c r="S8" s="54"/>
     </row>
     <row r="9" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="24">
         <v>7</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="23" t="s">
+      <c r="B9" s="125"/>
+      <c r="C9" s="113" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="J9" s="23" t="s">
+      <c r="I9" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="3">
         <v>20</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>3</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="11">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="11">
         <f t="shared" si="1"/>
         <v>7.5300000000000006E-2</v>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="11">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="5">
         <f t="shared" si="2"/>
         <v>0.502</v>
       </c>
-      <c r="S9" s="5"/>
+      <c r="S9" s="54"/>
     </row>
     <row r="10" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="24">
         <v>8</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="D10" s="23" t="s">
+      <c r="B10" s="125"/>
+      <c r="C10" s="113" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="I10" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J10" s="23" t="s">
+      <c r="I10" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="3">
         <v>30</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <v>4</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="11">
         <v>7.1800000000000003E-2</v>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="11">
         <f t="shared" si="1"/>
         <v>0.28720000000000001</v>
       </c>
-      <c r="Q10" s="22">
+      <c r="Q10" s="11">
         <v>7.1800000000000003E-2</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="5">
         <f t="shared" si="2"/>
         <v>2.1539999999999999</v>
       </c>
-      <c r="S10" s="5"/>
+      <c r="S10" s="54"/>
     </row>
     <row r="11" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="24">
         <v>9</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="32" t="s">
+      <c r="B11" s="125"/>
+      <c r="C11" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="27" t="s">
+      <c r="H11" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J11" s="23" t="s">
+      <c r="I11" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="3">
         <v>20</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <v>2</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="11">
         <v>2.69E-2</v>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="11">
         <f t="shared" si="1"/>
         <v>5.3800000000000001E-2</v>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11" s="11">
         <v>2.69E-2</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="5">
         <f t="shared" si="2"/>
         <v>0.53800000000000003</v>
       </c>
-      <c r="S11" s="5"/>
+      <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="24">
         <v>10</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="34" t="s">
+      <c r="B12" s="126"/>
+      <c r="C12" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="I12" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J12" s="35" t="s">
+      <c r="I12" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="J12" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="61">
         <v>50</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="62">
         <v>1</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="63">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="65">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="P12" s="22">
+      <c r="P12" s="65">
         <f t="shared" si="1"/>
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q12" s="22">
+      <c r="Q12" s="65">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="66">
         <f t="shared" si="2"/>
         <v>0.34499999999999997</v>
       </c>
-      <c r="S12" s="5"/>
+      <c r="S12" s="67"/>
     </row>
     <row r="13" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="24">
         <v>11</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J13" s="23" t="s">
+      <c r="H13" s="47" t="s">
+        <v>309</v>
+      </c>
+      <c r="I13" s="47" t="s">
         <v>308</v>
       </c>
-      <c r="K13" s="5">
+      <c r="J13" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="K13" s="48">
         <v>10</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="49">
         <v>1</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N13" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="O13" s="22">
+      <c r="N13" s="70" t="s">
+        <v>310</v>
+      </c>
+      <c r="O13" s="51">
         <v>0.16589999999999999</v>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="51">
         <f t="shared" si="1"/>
         <v>0.16589999999999999</v>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13" s="51">
         <v>0.16589999999999999</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="52">
         <f t="shared" si="2"/>
         <v>1.6589999999999998</v>
       </c>
-      <c r="S13" s="41" t="s">
-        <v>314</v>
+      <c r="S13" s="71" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="24">
         <v>12</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="125"/>
+      <c r="C14" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="I14" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K14" s="5">
+      <c r="I14" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K14" s="3">
         <v>7</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>1</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="11">
         <v>0.1825</v>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="11">
         <f t="shared" si="1"/>
         <v>0.1825</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="11">
         <v>0.1825</v>
       </c>
-      <c r="R14" s="7">
+      <c r="R14" s="5">
         <f t="shared" si="2"/>
         <v>1.2774999999999999</v>
       </c>
-      <c r="S14" s="41"/>
+      <c r="S14" s="72"/>
     </row>
     <row r="15" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="24">
         <v>13</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="23" t="s">
+      <c r="B15" s="126"/>
+      <c r="C15" s="116" t="s">
+        <v>279</v>
+      </c>
+      <c r="D15" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="I15" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K15" s="5">
+      <c r="I15" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="J15" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="K15" s="61">
         <v>20</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="75">
         <v>2</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="61">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="65">
         <v>7.5800000000000006E-2</v>
       </c>
-      <c r="P15" s="22">
+      <c r="P15" s="65">
         <f t="shared" si="1"/>
         <v>0.15160000000000001</v>
       </c>
-      <c r="Q15" s="22">
+      <c r="Q15" s="65">
         <v>7.5800000000000006E-2</v>
       </c>
-      <c r="R15" s="7">
+      <c r="R15" s="66">
         <f t="shared" si="2"/>
         <v>1.516</v>
       </c>
-      <c r="S15" s="41"/>
+      <c r="S15" s="77"/>
     </row>
     <row r="16" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="24">
         <v>14</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F16" s="23" t="s">
+      <c r="E16" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="F16" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="I16" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="J16" s="23" t="s">
+      <c r="I16" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="J16" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="48">
         <v>10</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="49">
         <v>1</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="51">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="51">
         <f t="shared" si="1"/>
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="Q16" s="22">
+      <c r="Q16" s="51">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="R16" s="7">
+      <c r="R16" s="52">
         <f t="shared" si="2"/>
         <v>0.52600000000000002</v>
       </c>
-      <c r="S16" s="41" t="s">
+      <c r="S16" s="71" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="24">
         <v>15</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="D17" s="35" t="s">
+      <c r="B17" s="125"/>
+      <c r="C17" s="117" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="F17" s="35" t="s">
+      <c r="E17" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="I17" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J17" s="35" t="s">
+      <c r="I17" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J17" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="3">
         <v>7</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="4">
         <v>1</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O17" s="22">
+      <c r="O17" s="11">
         <v>0.27629999999999999</v>
       </c>
-      <c r="P17" s="22">
+      <c r="P17" s="11">
         <f t="shared" si="1"/>
         <v>0.27629999999999999</v>
       </c>
-      <c r="Q17" s="22">
+      <c r="Q17" s="11">
         <v>0.27629999999999999</v>
       </c>
-      <c r="R17" s="7">
+      <c r="R17" s="5">
         <f t="shared" si="2"/>
         <v>1.9340999999999999</v>
       </c>
-      <c r="S17" s="41"/>
+      <c r="S17" s="72"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="A18" s="24">
         <v>16</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="32" t="s">
+      <c r="B18" s="125"/>
+      <c r="C18" s="112" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="I18" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J18" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="3">
         <v>10</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="4">
         <v>1</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N18" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="O18" s="22">
+      <c r="N18" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="11">
         <v>1.5</v>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="11">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="Q18" s="22">
+      <c r="Q18" s="11">
         <v>1.5</v>
       </c>
-      <c r="R18" s="7">
+      <c r="R18" s="5">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="S18" s="41" t="s">
-        <v>315</v>
+      <c r="S18" s="72" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="A19" s="24">
         <v>17</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="D19" s="23" t="s">
+      <c r="B19" s="126"/>
+      <c r="C19" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="78" t="s">
         <v>247</v>
       </c>
-      <c r="I19" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="I19" s="56" t="s">
+        <v>308</v>
+      </c>
+      <c r="J19" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="61">
         <v>10</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="75">
         <v>1</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="O19" s="22">
+      <c r="O19" s="65">
         <v>0.1167</v>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="65">
         <f t="shared" si="1"/>
         <v>0.1167</v>
       </c>
-      <c r="Q19" s="22">
+      <c r="Q19" s="65">
         <v>0.1167</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="66">
         <f t="shared" si="2"/>
         <v>1.167</v>
       </c>
-      <c r="S19" s="41"/>
+      <c r="S19" s="77"/>
     </row>
     <row r="20" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="24">
         <v>18</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="115" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="79" t="s">
         <v>248</v>
       </c>
-      <c r="I20" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K20" s="5">
+      <c r="I20" s="80" t="s">
+        <v>308</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="K20" s="48">
         <v>10</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="49">
         <v>1</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="51">
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="51">
         <f t="shared" si="1"/>
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="51">
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="R20" s="7">
+      <c r="R20" s="52">
         <f t="shared" si="2"/>
         <v>0.73099999999999998</v>
       </c>
-      <c r="S20" s="41" t="s">
+      <c r="S20" s="71" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="A21" s="24">
         <v>19</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="32" t="s">
+      <c r="B21" s="126"/>
+      <c r="C21" s="118" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="78" t="s">
         <v>249</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K21" s="5">
+      <c r="I21" s="56" t="s">
+        <v>308</v>
+      </c>
+      <c r="J21" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="K21" s="61">
         <v>7</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="75">
         <v>1</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="65">
         <v>0.41299999999999998</v>
       </c>
-      <c r="P21" s="22">
+      <c r="P21" s="65">
         <f t="shared" si="1"/>
         <v>0.41299999999999998</v>
       </c>
-      <c r="Q21" s="22">
+      <c r="Q21" s="65">
         <v>0.41299999999999998</v>
       </c>
-      <c r="R21" s="7">
+      <c r="R21" s="66">
         <f t="shared" si="2"/>
         <v>2.891</v>
       </c>
-      <c r="S21" s="5"/>
+      <c r="S21" s="67"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="24">
         <v>20</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="D22" s="23" t="s">
+      <c r="C22" s="119" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J22" s="23" t="s">
+      <c r="I22" s="80" t="s">
+        <v>308</v>
+      </c>
+      <c r="J22" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="48">
         <v>100</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="49">
         <v>6</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="48">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N22" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="O22" s="22">
+      <c r="O22" s="51">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="51">
         <f t="shared" si="1"/>
         <v>1.26E-2</v>
       </c>
-      <c r="Q22" s="22">
+      <c r="Q22" s="51">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="R22" s="7">
+      <c r="R22" s="52">
         <f t="shared" si="2"/>
         <v>0.21</v>
       </c>
-      <c r="S22" s="5"/>
+      <c r="S22" s="53"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="24">
         <v>21</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="23" t="s">
+      <c r="B23" s="125"/>
+      <c r="C23" s="113" t="s">
+        <v>283</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H23" s="27" t="s">
+      <c r="H23" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="I23" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="I23" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="3">
         <v>50</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="4">
         <v>1</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="11">
         <v>1.17E-2</v>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="11">
         <f t="shared" si="1"/>
         <v>1.17E-2</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="11">
         <v>1.17E-2</v>
       </c>
-      <c r="R23" s="7">
+      <c r="R23" s="5">
         <f t="shared" si="2"/>
         <v>0.58499999999999996</v>
       </c>
-      <c r="S23" s="5"/>
+      <c r="S23" s="54"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="A24" s="24">
         <v>22</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="D24" s="23" t="s">
+      <c r="B24" s="125"/>
+      <c r="C24" s="113" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J24" s="23" t="s">
+      <c r="I24" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J24" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="4">
         <v>1</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="11">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="P24" s="22">
+      <c r="P24" s="11">
         <f t="shared" si="1"/>
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q24" s="22">
+      <c r="Q24" s="11">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R24" s="7">
+      <c r="R24" s="5">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="S24" s="5"/>
+      <c r="S24" s="54"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="A25" s="24">
         <v>23</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="23" t="s">
+      <c r="B25" s="125"/>
+      <c r="C25" s="113" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="I25" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J25" s="23" t="s">
+      <c r="I25" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="3">
         <v>100</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="4">
         <v>1</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="N25" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="11">
         <v>3.3E-3</v>
       </c>
-      <c r="P25" s="22">
+      <c r="P25" s="11">
         <f t="shared" si="1"/>
         <v>3.3E-3</v>
       </c>
-      <c r="Q25" s="22">
+      <c r="Q25" s="11">
         <v>3.3E-3</v>
       </c>
-      <c r="R25" s="7">
+      <c r="R25" s="5">
         <f t="shared" si="2"/>
         <v>0.33</v>
       </c>
-      <c r="S25" s="5"/>
+      <c r="S25" s="54"/>
     </row>
     <row r="26" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="A26" s="24">
         <v>24</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D26" s="23" t="s">
+      <c r="B26" s="125"/>
+      <c r="C26" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H26" s="27" t="s">
+      <c r="H26" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J26" s="23" t="s">
+      <c r="I26" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J26" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="4">
         <v>1</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="N26" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="11">
         <v>1E-3</v>
       </c>
-      <c r="P26" s="22">
+      <c r="P26" s="11">
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26" s="11">
         <v>1E-3</v>
       </c>
-      <c r="R26" s="7">
+      <c r="R26" s="5">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S26" s="5"/>
+      <c r="S26" s="54"/>
     </row>
     <row r="27" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="A27" s="24">
         <v>25</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="32" t="s">
+      <c r="B27" s="125"/>
+      <c r="C27" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="I27" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="J27" s="23" t="s">
+      <c r="I27" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="4">
         <v>1</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N27" s="4" t="s">
+      <c r="N27" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="11">
         <v>1E-3</v>
       </c>
-      <c r="P27" s="22">
+      <c r="P27" s="11">
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="Q27" s="22">
+      <c r="Q27" s="11">
         <v>1E-3</v>
       </c>
-      <c r="R27" s="7">
+      <c r="R27" s="5">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S27" s="5"/>
+      <c r="S27" s="54"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="A28" s="24">
         <v>26</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="D28" s="23" t="s">
+      <c r="B28" s="125"/>
+      <c r="C28" s="113" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="I28" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J28" s="23" t="s">
+      <c r="I28" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J28" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="3">
         <v>100</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="4">
         <v>1</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="N28" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="11">
         <v>1E-3</v>
       </c>
-      <c r="P28" s="22">
+      <c r="P28" s="11">
         <f t="shared" si="1"/>
         <v>1E-3</v>
       </c>
-      <c r="Q28" s="22">
+      <c r="Q28" s="11">
         <v>1E-3</v>
       </c>
-      <c r="R28" s="7">
+      <c r="R28" s="5">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S28" s="5"/>
+      <c r="S28" s="54"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="A29" s="24">
         <v>27</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="D29" s="23" t="s">
+      <c r="B29" s="125"/>
+      <c r="C29" s="113" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="G29" s="24" t="s">
+      <c r="G29" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="27" t="s">
+      <c r="H29" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="I29" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J29" s="23" t="s">
+      <c r="I29" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J29" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="4">
         <v>2</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O29" s="22">
+      <c r="O29" s="11">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="P29" s="22">
+      <c r="P29" s="11">
         <f t="shared" si="1"/>
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="Q29" s="22">
+      <c r="Q29" s="11">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="R29" s="7">
+      <c r="R29" s="5">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="S29" s="5"/>
+      <c r="S29" s="54"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="A30" s="24">
         <v>28</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="D30" s="23" t="s">
+      <c r="B30" s="125"/>
+      <c r="C30" s="113" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H30" s="27" t="s">
+      <c r="H30" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="I30" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J30" s="23" t="s">
+      <c r="I30" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J30" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="3">
         <v>100</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="4">
         <v>1</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="N30" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="11">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="P30" s="22">
+      <c r="P30" s="11">
         <f t="shared" si="1"/>
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q30" s="22">
+      <c r="Q30" s="11">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R30" s="7">
+      <c r="R30" s="5">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="S30" s="5"/>
+      <c r="S30" s="54"/>
     </row>
     <row r="31" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="A31" s="24">
         <v>29</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="32" t="s">
+      <c r="B31" s="125"/>
+      <c r="C31" s="112" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="24" t="s">
+      <c r="G31" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="I31" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J31" s="23" t="s">
+      <c r="I31" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J31" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="3">
         <v>100</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="4">
         <v>1</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N31" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="11">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="P31" s="22">
+      <c r="P31" s="11">
         <f t="shared" si="1"/>
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q31" s="22">
+      <c r="Q31" s="11">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R31" s="7">
+      <c r="R31" s="5">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S31" s="5"/>
+      <c r="S31" s="54"/>
     </row>
     <row r="32" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="A32" s="24">
         <v>30</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="D32" s="23" t="s">
+      <c r="B32" s="125"/>
+      <c r="C32" s="113" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H32" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="I32" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J32" s="23" t="s">
+      <c r="I32" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="3">
         <v>20</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="4">
         <v>1</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="N32" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O32" s="22">
+      <c r="O32" s="11">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="P32" s="22">
+      <c r="P32" s="11">
         <f t="shared" si="1"/>
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="Q32" s="22">
+      <c r="Q32" s="11">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="R32" s="7">
+      <c r="R32" s="5">
         <f t="shared" si="2"/>
         <v>0.45400000000000001</v>
       </c>
-      <c r="S32" s="5"/>
+      <c r="S32" s="54"/>
     </row>
     <row r="33" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="A33" s="24">
         <v>31</v>
       </c>
-      <c r="B33" s="51"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="125"/>
+      <c r="C33" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="G33" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H33" s="27" t="s">
+      <c r="H33" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="I33" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J33" s="23" t="s">
+      <c r="I33" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="J33" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="4">
         <v>1</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N33" s="4" t="s">
+      <c r="N33" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O33" s="22">
+      <c r="O33" s="11">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="P33" s="22">
+      <c r="P33" s="11">
         <f t="shared" si="1"/>
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q33" s="22">
+      <c r="Q33" s="11">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="R33" s="7">
+      <c r="R33" s="5">
         <f t="shared" si="2"/>
         <v>0.16999999999999998</v>
       </c>
-      <c r="S33" s="5"/>
+      <c r="S33" s="54"/>
     </row>
     <row r="34" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+      <c r="A34" s="24">
         <v>32</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="D34" s="23" t="s">
+      <c r="B34" s="126"/>
+      <c r="C34" s="116" t="s">
+        <v>291</v>
+      </c>
+      <c r="D34" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H34" s="74" t="s">
         <v>261</v>
       </c>
-      <c r="I34" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J34" s="23" t="s">
+      <c r="I34" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="J34" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="61">
         <v>50</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="75">
         <v>1</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="N34" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="O34" s="22">
+      <c r="O34" s="65">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="P34" s="22">
+      <c r="P34" s="65">
         <f t="shared" si="1"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="Q34" s="22">
+      <c r="Q34" s="65">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="R34" s="7">
+      <c r="R34" s="66">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="S34" s="5"/>
+      <c r="S34" s="67"/>
     </row>
     <row r="35" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="A35" s="24">
         <v>33</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="C35" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E35" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F35" s="23" t="s">
+      <c r="E35" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="F35" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H35" s="27" t="s">
+      <c r="H35" s="68" t="s">
         <v>262</v>
       </c>
-      <c r="I35" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="J35" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K35" s="5">
+      <c r="I35" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="J35" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="K35" s="39">
         <v>7</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="40">
         <v>1</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="N35" s="69" t="s">
         <v>236</v>
       </c>
-      <c r="O35" s="22">
+      <c r="O35" s="41">
         <v>0.47610000000000002</v>
       </c>
-      <c r="P35" s="22">
+      <c r="P35" s="41">
         <f t="shared" si="1"/>
         <v>0.47610000000000002</v>
       </c>
-      <c r="Q35" s="22">
+      <c r="Q35" s="41">
         <v>0.47610000000000002</v>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="42">
         <f t="shared" si="2"/>
         <v>3.3327</v>
       </c>
-      <c r="S35" s="5"/>
+      <c r="S35" s="129"/>
     </row>
     <row r="36" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="A36" s="24">
         <v>34</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="128" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="D36" s="43" t="s">
+      <c r="C36" s="121" t="s">
+        <v>292</v>
+      </c>
+      <c r="D36" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="E36" s="43" t="s">
-        <v>300</v>
-      </c>
-      <c r="F36" s="43" t="s">
+      <c r="E36" s="87" t="s">
+        <v>297</v>
+      </c>
+      <c r="F36" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="G36" s="44" t="s">
+      <c r="G36" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J36" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="K36" s="46">
-        <v>85</v>
-      </c>
-      <c r="L36" s="47">
+      <c r="H36" s="89" t="s">
+        <v>315</v>
+      </c>
+      <c r="I36" s="89" t="s">
+        <v>299</v>
+      </c>
+      <c r="J36" s="87" t="s">
+        <v>306</v>
+      </c>
+      <c r="K36" s="90">
+        <v>7</v>
+      </c>
+      <c r="L36" s="91">
         <v>1</v>
       </c>
-      <c r="M36" s="46">
+      <c r="M36" s="90">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N36" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="O36" s="49">
-        <v>0.59699999999999998</v>
-      </c>
-      <c r="P36" s="49">
+      <c r="N36" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="O36" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="P36" s="93">
         <f t="shared" si="1"/>
-        <v>0.59699999999999998</v>
-      </c>
-      <c r="Q36" s="49">
-        <v>0.59699999999999998</v>
-      </c>
-      <c r="R36" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="Q36" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="R36" s="94">
         <f t="shared" si="2"/>
-        <v>50.744999999999997</v>
-      </c>
-      <c r="S36" s="41" t="s">
+        <v>3.5</v>
+      </c>
+      <c r="S36" s="130" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="A37" s="24">
         <v>35</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="124" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F37" s="23" t="s">
+      <c r="E37" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="F37" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="G37" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="H37" s="27" t="s">
+      <c r="G37" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="H37" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="I37" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J37" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K37" s="5">
+      <c r="I37" s="47" t="s">
+        <v>299</v>
+      </c>
+      <c r="J37" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="K37" s="48">
         <v>6</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="49">
         <v>1</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N37" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="O37" s="22">
-        <v>3.3721999999999999</v>
-      </c>
-      <c r="P37" s="22">
+      <c r="N37" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="O37" s="51">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="P37" s="51">
         <f t="shared" si="1"/>
-        <v>3.3721999999999999</v>
-      </c>
-      <c r="Q37" s="22">
-        <v>3.3721999999999999</v>
-      </c>
-      <c r="R37" s="7">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="Q37" s="51">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="R37" s="52">
         <f t="shared" si="2"/>
-        <v>20.2332</v>
-      </c>
-      <c r="S37" s="5"/>
+        <v>18.282</v>
+      </c>
+      <c r="S37" s="71" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="38" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="A38" s="24">
         <v>36</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="32" t="s">
-        <v>296</v>
-      </c>
-      <c r="D38" s="23" t="s">
+      <c r="B38" s="125"/>
+      <c r="C38" s="112" t="s">
+        <v>293</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="27" t="s">
+      <c r="H38" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="I38" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J38" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K38" s="5">
+      <c r="I38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K38" s="3">
         <v>6</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="4">
         <v>1</v>
       </c>
-      <c r="M38" s="5">
+      <c r="M38" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N38" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="O38" s="22">
-        <v>1.6869000000000001</v>
-      </c>
-      <c r="P38" s="22">
+      <c r="N38" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="O38" s="11">
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="P38" s="11">
         <f t="shared" si="1"/>
-        <v>1.6869000000000001</v>
-      </c>
-      <c r="Q38" s="22">
-        <v>1.6869000000000001</v>
-      </c>
-      <c r="R38" s="7">
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="Q38" s="11">
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="R38" s="5">
         <f t="shared" si="2"/>
-        <v>10.121400000000001</v>
-      </c>
-      <c r="S38" s="5"/>
+        <v>7.032</v>
+      </c>
+      <c r="S38" s="72" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="39" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="A39" s="24">
         <v>37</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="58" t="s">
+      <c r="B39" s="125"/>
+      <c r="C39" s="117" t="s">
         <v>165</v>
       </c>
-      <c r="D39" s="43" t="s">
+      <c r="D39" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E39" s="43" t="s">
+      <c r="E39" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F39" s="43" t="s">
+      <c r="F39" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G39" s="44" t="s">
+      <c r="G39" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J39" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="K39" s="46">
-        <v>5</v>
-      </c>
-      <c r="L39" s="47">
+      <c r="H39" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="K39" s="26">
+        <v>6</v>
+      </c>
+      <c r="L39" s="27">
         <v>1</v>
       </c>
-      <c r="M39" s="46">
+      <c r="M39" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N39" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="O39" s="49">
-        <v>16.577000000000002</v>
-      </c>
-      <c r="P39" s="49">
+      <c r="N39" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="O39" s="29">
+        <v>10.156000000000001</v>
+      </c>
+      <c r="P39" s="29">
         <f t="shared" si="1"/>
-        <v>16.577000000000002</v>
-      </c>
-      <c r="Q39" s="49">
-        <v>16.577000000000002</v>
-      </c>
-      <c r="R39" s="50">
+        <v>10.156000000000001</v>
+      </c>
+      <c r="Q39" s="29">
+        <v>10.156000000000001</v>
+      </c>
+      <c r="R39" s="30">
         <f t="shared" si="2"/>
-        <v>82.885000000000005</v>
-      </c>
-      <c r="S39" s="41" t="s">
+        <v>60.936000000000007</v>
+      </c>
+      <c r="S39" s="72" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="A40" s="24">
         <v>38</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="58" t="s">
+      <c r="B40" s="125"/>
+      <c r="C40" s="117" t="s">
         <v>170</v>
       </c>
-      <c r="D40" s="43" t="s">
+      <c r="D40" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="E40" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F40" s="43" t="s">
+      <c r="F40" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="G40" s="44" t="s">
+      <c r="G40" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J40" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="K40" s="46">
-        <v>750</v>
-      </c>
-      <c r="L40" s="47">
+      <c r="H40" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="K40" s="26">
+        <v>6</v>
+      </c>
+      <c r="L40" s="27">
         <v>1</v>
       </c>
-      <c r="M40" s="46">
+      <c r="M40" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N40" s="48" t="s">
-        <v>276</v>
-      </c>
-      <c r="O40" s="49">
-        <v>0.496</v>
-      </c>
-      <c r="P40" s="49">
+      <c r="N40" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="O40" s="29">
+        <v>1.5409999999999999</v>
+      </c>
+      <c r="P40" s="29">
         <f t="shared" si="1"/>
-        <v>0.496</v>
-      </c>
-      <c r="Q40" s="49">
-        <v>0.496</v>
-      </c>
-      <c r="R40" s="50">
+        <v>1.5409999999999999</v>
+      </c>
+      <c r="Q40" s="29">
+        <v>1.5409999999999999</v>
+      </c>
+      <c r="R40" s="30">
         <f t="shared" si="2"/>
-        <v>372</v>
-      </c>
-      <c r="S40" s="41" t="s">
+        <v>9.2459999999999987</v>
+      </c>
+      <c r="S40" s="72" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="A41" s="24">
         <v>39</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="32" t="s">
+      <c r="B41" s="125"/>
+      <c r="C41" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E41" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="G41" s="24" t="s">
+      <c r="G41" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="H41" s="24"/>
-      <c r="I41" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J41" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K41" s="5">
-        <v>22</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="H41" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K41" s="3">
+        <v>6</v>
+      </c>
+      <c r="L41" s="4">
         <v>1</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N41" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="O41" s="22">
-        <v>0.72753000000000001</v>
-      </c>
-      <c r="P41" s="22">
+      <c r="N41" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="O41" s="11">
+        <v>1</v>
+      </c>
+      <c r="P41" s="11">
         <f t="shared" si="1"/>
-        <v>0.72753000000000001</v>
-      </c>
-      <c r="Q41" s="22">
-        <v>0.72753000000000001</v>
-      </c>
-      <c r="R41" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>1</v>
+      </c>
+      <c r="R41" s="5">
         <f t="shared" si="2"/>
-        <v>16.005659999999999</v>
-      </c>
-      <c r="S41" s="41" t="s">
-        <v>321</v>
+        <v>6</v>
+      </c>
+      <c r="S41" s="72" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="A42" s="24">
         <v>40</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="D42" s="23" t="s">
+      <c r="B42" s="125"/>
+      <c r="C42" s="112" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="H42" s="27" t="s">
+      <c r="H42" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="I42" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J42" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K42" s="5">
+      <c r="I42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K42" s="3">
         <v>6</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="4">
         <v>1</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N42" s="21" t="s">
+      <c r="N42" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="11">
         <v>0.32269999999999999</v>
       </c>
-      <c r="P42" s="22">
+      <c r="P42" s="11">
         <f t="shared" si="1"/>
         <v>0.32269999999999999</v>
       </c>
-      <c r="Q42" s="22">
+      <c r="Q42" s="11">
         <v>0.32269999999999999</v>
       </c>
-      <c r="R42" s="7">
+      <c r="R42" s="5">
         <f t="shared" si="2"/>
         <v>1.9361999999999999</v>
       </c>
-      <c r="S42" s="5"/>
+      <c r="S42" s="54"/>
     </row>
     <row r="43" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="A43" s="24">
         <v>41</v>
       </c>
-      <c r="B43" s="51"/>
-      <c r="C43" s="32" t="s">
+      <c r="B43" s="125"/>
+      <c r="C43" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E43" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="F43" s="23" t="s">
+      <c r="F43" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="24" t="s">
+      <c r="G43" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="H43" s="24"/>
-      <c r="I43" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K43" s="5">
-        <v>10</v>
-      </c>
-      <c r="L43" s="6">
+      <c r="H43" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K43" s="3">
+        <v>6</v>
+      </c>
+      <c r="L43" s="4">
         <v>1</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N43" s="4"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="22">
+      <c r="N43" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="O43" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="P43" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="R43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="5" t="s">
-        <v>322</v>
+        <v>7.5</v>
+      </c>
+      <c r="S43" s="72" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="A44" s="24">
         <v>42</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="32" t="s">
+      <c r="B44" s="125"/>
+      <c r="C44" s="112" t="s">
         <v>188</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="H44" s="27" t="s">
+      <c r="H44" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="I44" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J44" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K44" s="5">
+      <c r="I44" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K44" s="3">
         <v>6</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="4">
         <v>1</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N44" s="4" t="s">
+      <c r="N44" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="11">
         <v>0.30990000000000001</v>
       </c>
-      <c r="P44" s="22">
+      <c r="P44" s="11">
         <f t="shared" si="1"/>
         <v>0.30990000000000001</v>
       </c>
-      <c r="Q44" s="22">
+      <c r="Q44" s="11">
         <v>0.30990000000000001</v>
       </c>
-      <c r="R44" s="7">
+      <c r="R44" s="5">
         <f t="shared" si="2"/>
         <v>1.8593999999999999</v>
       </c>
-      <c r="S44" s="5"/>
+      <c r="S44" s="54"/>
     </row>
     <row r="45" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="A45" s="24">
         <v>43</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="32" t="s">
+      <c r="B45" s="126"/>
+      <c r="C45" s="118" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="F45" s="23" t="s">
+      <c r="F45" s="55" t="s">
         <v>195</v>
       </c>
-      <c r="G45" s="24" t="s">
+      <c r="G45" s="73" t="s">
         <v>196</v>
       </c>
-      <c r="H45" s="27"/>
-      <c r="I45" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J45" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K45" s="5">
-        <v>5</v>
-      </c>
-      <c r="L45" s="6">
+      <c r="H45" s="55" t="s">
+        <v>315</v>
+      </c>
+      <c r="I45" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="J45" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="K45" s="61">
+        <v>6</v>
+      </c>
+      <c r="L45" s="75">
         <v>1</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N45" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="O45" s="22">
-        <v>1.7248000000000001</v>
-      </c>
-      <c r="P45" s="22">
+      <c r="N45" s="76" t="s">
+        <v>313</v>
+      </c>
+      <c r="O45" s="65">
+        <v>2.835</v>
+      </c>
+      <c r="P45" s="65">
         <f t="shared" si="1"/>
-        <v>1.7248000000000001</v>
-      </c>
-      <c r="Q45" s="22">
-        <v>1.7248000000000001</v>
-      </c>
-      <c r="R45" s="7">
+        <v>2.835</v>
+      </c>
+      <c r="Q45" s="65">
+        <v>2.835</v>
+      </c>
+      <c r="R45" s="66">
         <f t="shared" si="2"/>
-        <v>8.6240000000000006</v>
-      </c>
-      <c r="S45" s="5" t="s">
-        <v>275</v>
+        <v>17.009999999999998</v>
+      </c>
+      <c r="S45" s="72" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="A46" s="24">
         <v>44</v>
       </c>
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="124" t="s">
         <v>197</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="115" t="s">
         <v>198</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="E46" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F46" s="23" t="s">
+      <c r="E46" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="F46" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G46" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H46" s="27" t="s">
+      <c r="H46" s="46" t="s">
         <v>267</v>
       </c>
-      <c r="I46" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J46" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K46" s="5">
+      <c r="I46" s="47" t="s">
+        <v>299</v>
+      </c>
+      <c r="J46" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="K46" s="48">
         <v>7</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="49">
         <v>1</v>
       </c>
-      <c r="M46" s="5">
+      <c r="M46" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="N46" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="O46" s="22">
+      <c r="O46" s="51">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="P46" s="22">
+      <c r="P46" s="51">
         <f t="shared" si="1"/>
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="Q46" s="22">
+      <c r="Q46" s="51">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="R46" s="7">
+      <c r="R46" s="52">
         <f t="shared" si="2"/>
         <v>0.63840000000000008</v>
       </c>
-      <c r="S46" s="5"/>
+      <c r="S46" s="53"/>
     </row>
     <row r="47" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+      <c r="A47" s="24">
         <v>45</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="32" t="s">
-        <v>298</v>
-      </c>
-      <c r="D47" s="23" t="s">
+      <c r="B47" s="125"/>
+      <c r="C47" s="112" t="s">
+        <v>295</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E47" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F47" s="23" t="s">
+      <c r="E47" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G47" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="H47" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="I47" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J47" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K47" s="5">
+      <c r="H47" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K47" s="3">
         <v>7</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="4">
         <v>1</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="3">
         <f>L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="O47" s="22">
+      <c r="N47" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="O47" s="11">
         <v>8.8000000000000007</v>
       </c>
-      <c r="P47" s="22">
+      <c r="P47" s="11">
         <f t="shared" si="1"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="Q47" s="22">
+      <c r="Q47" s="11">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R47" s="7">
+      <c r="R47" s="5">
         <f t="shared" si="2"/>
         <v>61.600000000000009</v>
       </c>
-      <c r="S47" s="18" t="s">
+      <c r="S47" s="81" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+      <c r="A48" s="24">
         <v>46</v>
       </c>
-      <c r="B48" s="51"/>
-      <c r="C48" s="32" t="s">
+      <c r="B48" s="125"/>
+      <c r="C48" s="112" t="s">
         <v>206</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="E48" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F48" s="23" t="s">
+      <c r="E48" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F48" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="G48" s="24" t="s">
+      <c r="G48" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="H48" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="I48" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J48" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K48" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="L48" s="6">
+      <c r="H48" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="L48" s="4">
         <v>1</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="3">
         <f>L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="O48" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="P48" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q48" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="R48" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="S48" s="11" t="s">
+      <c r="N48" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="O48" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="P48" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q48" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R48" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="S48" s="82" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="A49" s="24">
         <v>47</v>
       </c>
-      <c r="B49" s="51"/>
-      <c r="C49" s="32" t="s">
+      <c r="B49" s="125"/>
+      <c r="C49" s="112" t="s">
         <v>211</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D49" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="F49" s="23" t="s">
+      <c r="F49" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="G49" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H49" s="24"/>
-      <c r="I49" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J49" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="6">
+      <c r="G49" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="L49" s="4">
         <v>1</v>
       </c>
-      <c r="M49" s="5">
+      <c r="M49" s="3">
         <f>L49*5</f>
         <v>5</v>
       </c>
-      <c r="N49" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="O49" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="P49" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q49" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="R49" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="S49" s="11" t="s">
+      <c r="N49" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="O49" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q49" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R49" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="S49" s="82" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="A50" s="24">
         <v>48</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="32" t="s">
+      <c r="B50" s="125"/>
+      <c r="C50" s="112" t="s">
         <v>214</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="G50" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H50" s="24"/>
-      <c r="I50" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="6">
+      <c r="G50" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="L50" s="4">
         <v>2</v>
       </c>
-      <c r="M50" s="5">
+      <c r="M50" s="3">
         <f>L50*5</f>
         <v>10</v>
       </c>
-      <c r="N50" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="O50" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="P50" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q50" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="R50" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="S50" s="11" t="s">
+      <c r="N50" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="O50" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="P50" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q50" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R50" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="S50" s="82" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="A51" s="24">
         <v>49</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="32" t="s">
+      <c r="B51" s="125"/>
+      <c r="C51" s="112" t="s">
         <v>217</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="23" t="s">
+      <c r="E51" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="F51" s="23" t="s">
+      <c r="F51" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="G51" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H51" s="24"/>
-      <c r="I51" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="6">
+      <c r="G51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K51" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="L51" s="4">
         <v>1</v>
       </c>
-      <c r="M51" s="5">
+      <c r="M51" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N51" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="O51" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="P51" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q51" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="R51" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="S51" s="11" t="s">
+      <c r="N51" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="O51" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="P51" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q51" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R51" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="S51" s="82" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="A52" s="24">
         <v>50</v>
       </c>
-      <c r="B52" s="52"/>
-      <c r="C52" s="37" t="s">
+      <c r="B52" s="126"/>
+      <c r="C52" s="122" t="s">
         <v>220</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="83" t="s">
         <v>221</v>
       </c>
-      <c r="E52" s="23" t="s">
+      <c r="E52" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="F52" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="G52" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H52" s="24"/>
-      <c r="I52" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="6">
+      <c r="G52" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="H52" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="I52" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="J52" s="55" t="s">
+        <v>306</v>
+      </c>
+      <c r="K52" s="133" t="s">
+        <v>315</v>
+      </c>
+      <c r="L52" s="75">
         <v>14</v>
       </c>
-      <c r="M52" s="5">
+      <c r="M52" s="61">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="N52" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="O52" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="P52" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q52" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="R52" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="S52" s="11" t="s">
+      <c r="N52" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="O52" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="P52" s="85" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q52" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="R52" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="S52" s="86" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+      <c r="A53" s="24">
         <v>51</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="109" t="s">
         <v>224</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="E53" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F53" s="24" t="s">
+      <c r="E53" s="96" t="s">
+        <v>297</v>
+      </c>
+      <c r="F53" s="96" t="s">
         <v>225</v>
       </c>
-      <c r="G53" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H53" s="24"/>
-      <c r="I53" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J53" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5">
+      <c r="G53" s="97" t="s">
+        <v>299</v>
+      </c>
+      <c r="H53" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="I53" s="97" t="s">
+        <v>299</v>
+      </c>
+      <c r="J53" s="95" t="s">
+        <v>306</v>
+      </c>
+      <c r="K53" s="134" t="s">
+        <v>315</v>
+      </c>
+      <c r="L53" s="98">
         <v>1</v>
       </c>
-      <c r="M53" s="5">
+      <c r="M53" s="98">
         <v>3</v>
       </c>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="12"/>
-      <c r="Q53" s="12"/>
-      <c r="R53" s="12"/>
-      <c r="S53" s="11" t="s">
+      <c r="N53" s="99"/>
+      <c r="O53" s="99"/>
+      <c r="P53" s="100"/>
+      <c r="Q53" s="100"/>
+      <c r="R53" s="100"/>
+      <c r="S53" s="131" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+    <row r="54" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="132">
         <v>52</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="110" t="s">
         <v>227</v>
       </c>
-      <c r="C54" s="38"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="H54" s="24"/>
-      <c r="I54" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J54" s="38"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
-      <c r="R54" s="12"/>
-      <c r="S54" s="11" t="s">
+      <c r="C54" s="123"/>
+      <c r="D54" s="102"/>
+      <c r="E54" s="103" t="s">
+        <v>297</v>
+      </c>
+      <c r="F54" s="103"/>
+      <c r="G54" s="104" t="s">
+        <v>299</v>
+      </c>
+      <c r="H54" s="104" t="s">
+        <v>315</v>
+      </c>
+      <c r="I54" s="104" t="s">
+        <v>299</v>
+      </c>
+      <c r="J54" s="101"/>
+      <c r="K54" s="135" t="s">
+        <v>315</v>
+      </c>
+      <c r="L54" s="105"/>
+      <c r="M54" s="105"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="106"/>
+      <c r="P54" s="107"/>
+      <c r="Q54" s="107"/>
+      <c r="R54" s="107"/>
+      <c r="S54" s="108" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="53" t="s">
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="16"/>
-      <c r="R55" s="16">
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="7"/>
+      <c r="R55" s="7">
         <f>SUM(R3:R48)</f>
-        <v>667.43756000000019</v>
-      </c>
-      <c r="S55" s="15"/>
+        <v>236.32930000000005</v>
+      </c>
+      <c r="S55" s="6"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="54" t="s">
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="16">
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="7">
         <f>SUM(P3:P48)</f>
-        <v>39.207130000000006</v>
-      </c>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="16">
+        <v>35.526700000000005</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="7">
         <f>R55/5</f>
-        <v>133.48751200000004</v>
-      </c>
-      <c r="S56" s="15"/>
+        <v>47.265860000000011</v>
+      </c>
+      <c r="S56" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4871,7 +5440,7 @@
     <mergeCell ref="B22:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="N56:P56">
-    <cfRule type="dataBar" priority="9">
+    <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4885,7 +5454,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N41 N43:N46">
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4899,7 +5468,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P54">
-    <cfRule type="dataBar" priority="7">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4913,7 +5482,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:M54">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4925,7 +5494,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q53:Q54">
-    <cfRule type="dataBar" priority="5">
+    <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4939,7 +5508,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q47">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4953,7 +5522,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O47">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4967,7 +5536,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P56:R56">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4981,7 +5550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R3:R47">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5021,42 +5590,35 @@
     <hyperlink ref="N33" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="N34" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="N35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N37" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N42" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="N44" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="N46" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="N4" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N5" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N9" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="N16" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="N27" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="N39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="N45" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N40" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="G11" r:id="rId41" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="G12" r:id="rId42" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="G6" r:id="rId43" display="https://lcsc.com/brand-detail/79.html" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="G31" r:id="rId44" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="G44" r:id="rId45" display="https://lcsc.com/brand-detail/296.html" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="G42" r:id="rId46" display="https://lcsc.com/brand-detail/488.html" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="G41" r:id="rId47" display="https://lcsc.com/brand-detail/897.html" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="G38" r:id="rId48" display="https://lcsc.com/brand-detail/11667.html" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="G28" r:id="rId49" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="G26" r:id="rId50" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="G25" r:id="rId51" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="G22" r:id="rId52" display="https://lcsc.com/brand-detail/512.html" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="G17" r:id="rId53" display="https://lcsc.com/brand-detail/11934.html" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="G32" r:id="rId54" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="G47" r:id="rId55" tooltip="Magnetic Connectors from HytePro" display="https://www.hyte.pro/" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="N13" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="N18" r:id="rId57" xr:uid="{53747EDB-C048-45B7-9C78-F6304C078768}"/>
-    <hyperlink ref="N41" r:id="rId58" xr:uid="{B18DA18F-9AAF-44CD-873B-8AEAF6EDDE80}"/>
-    <hyperlink ref="N47" r:id="rId59" xr:uid="{6110106C-4E98-41F9-962F-9787978B565A}"/>
+    <hyperlink ref="N42" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N44" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N4" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N5" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N9" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N16" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N27" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="G11" r:id="rId35" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="G12" r:id="rId36" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="G6" r:id="rId37" display="https://lcsc.com/brand-detail/79.html" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="G31" r:id="rId38" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="G44" r:id="rId39" display="https://lcsc.com/brand-detail/296.html" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="G42" r:id="rId40" display="https://lcsc.com/brand-detail/488.html" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="G41" r:id="rId41" display="https://lcsc.com/brand-detail/897.html" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="G38" r:id="rId42" display="https://lcsc.com/brand-detail/11667.html" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="G28" r:id="rId43" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="G26" r:id="rId44" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="G25" r:id="rId45" display="https://lcsc.com/brand-detail/99.html" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="G22" r:id="rId46" display="https://lcsc.com/brand-detail/512.html" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="G17" r:id="rId47" display="https://lcsc.com/brand-detail/11934.html" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="G32" r:id="rId48" display="https://www.digikey.com/en/supplier-centers/murata-electronics" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="G47" r:id="rId49" tooltip="Magnetic Connectors from HytePro" display="https://www.hyte.pro/" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N13" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N18" r:id="rId51" xr:uid="{53747EDB-C048-45B7-9C78-F6304C078768}"/>
+    <hyperlink ref="N47" r:id="rId52" xr:uid="{6110106C-4E98-41F9-962F-9787978B565A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId60"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
